--- a/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación, discapacidad física</t>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,52</t>
+          <t>2,79; 9,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,2</t>
+          <t>0,47; 4,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,02</t>
+          <t>0,59; 5,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,91</t>
+          <t>3,56; 11,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,49</t>
+          <t>0,51; 3,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,9</t>
+          <t>0,62; 3,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,64</t>
+          <t>3,98; 9,11</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,89</t>
+          <t>2,06; 7,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,17</t>
+          <t>0,91; 5,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,71</t>
+          <t>2,2; 6,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,31</t>
+          <t>1,87; 7,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,25</t>
+          <t>1,72; 6,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,01</t>
+          <t>0,95; 4,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,13</t>
+          <t>4,85; 11,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,53</t>
+          <t>1,47; 4,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,18</t>
+          <t>2,41; 6,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,87</t>
+          <t>1,4; 4,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,22</t>
+          <t>4,22; 8,25</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,72</t>
+          <t>1,21; 6,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 10,39</t>
+          <t>3,25; 9,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,68</t>
+          <t>1,8; 8,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,9</t>
+          <t>2,04; 7,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,3</t>
+          <t>0,82; 6,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 15,05</t>
+          <t>3,01; 14,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,25</t>
+          <t>2,05; 6,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,82</t>
+          <t>1,37; 4,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,63</t>
+          <t>0,52; 3,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 10,1</t>
+          <t>3,99; 10,63</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,75</t>
+          <t>0,48; 4,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,88</t>
+          <t>1,72; 7,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 9,59</t>
+          <t>3,04; 9,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,31</t>
+          <t>2,86; 8,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,16</t>
+          <t>1,69; 6,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,24</t>
+          <t>1,83; 7,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,4</t>
+          <t>1,05; 5,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,05</t>
+          <t>1,3; 6,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,59</t>
+          <t>1,48; 4,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,37</t>
+          <t>2,31; 6,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,84</t>
+          <t>2,55; 6,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,0</t>
+          <t>2,48; 5,96</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,97</t>
+          <t>0,96; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,25</t>
+          <t>1,76; 4,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,16</t>
+          <t>1,55; 4,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,84</t>
+          <t>3,72; 6,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,87</t>
+          <t>2,24; 4,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,99</t>
+          <t>2,48; 5,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,41</t>
+          <t>1,32; 3,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,44</t>
+          <t>4,59; 8,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,55</t>
+          <t>1,95; 3,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,11</t>
+          <t>2,33; 4,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,3</t>
+          <t>1,72; 3,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,95</t>
+          <t>4,59; 7,0</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6364</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2151</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>9343</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3427</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3446</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>15706</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4175</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4278</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3275; 10966</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>555; 5644</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>667; 6488</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3721</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5002; 16245</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1140; 7042</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1309; 7568</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3427</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>10256; 23479</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5784</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3801</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7686</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5836</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5658</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4161</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>19301</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7049</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11441</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7962</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>26988</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4211</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2658; 9893</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1383; 7633</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4195; 12536</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2629; 10986</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2657; 10521</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1661; 8524</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12364; 28533</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3895; 12145</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>6843; 17702</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4578; 13502</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>18793; 36780</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11600</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4819</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4955</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3483</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>11825</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8123</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6046</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4084</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>23426</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1301; 7382</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4016</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2974</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6183; 18552</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2027; 9345</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2384; 9189</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1091; 9182</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5575; 26171</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4526; 13993</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3040; 10822</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1295; 8777</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>14994; 39952</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3155</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5661</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8474</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5728</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5644</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8617</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11388</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13680</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>14118</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>798; 7891</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2517; 11334</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5069; 16162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4803; 13652</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2658; 9953</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2835; 11308</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1665; 8981</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2360; 11395</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4786; 14425</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>6958; 18916</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8277; 20814</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>8668; 20827</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8948</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13156</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13758</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34124</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18269</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19165</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12645</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>46113</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>27217</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32322</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26402</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>80237</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4835; 14749</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8417; 21328</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8157; 21193</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>24780; 44047</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11828; 25565</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13359; 27717</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7533; 18987</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>34970; 62420</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>20139; 37367</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>23632; 41632</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18841; 36896</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>65572; 100011</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,37 +732,37 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,35</t>
+          <t>2,8; 9,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,77</t>
+          <t>0,47; 5,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,77</t>
+          <t>0,74; 6,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,57</t>
+          <t>3,36; 11,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,15</t>
+          <t>0,52; 3,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,61</t>
+          <t>0,62; 4,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,11</t>
+          <t>3,93; 9,09</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,67</t>
+          <t>2,1; 8,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,02</t>
+          <t>0,92; 5,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,58</t>
+          <t>2,15; 6,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,81</t>
+          <t>2,18; 7,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,81</t>
+          <t>1,77; 6,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,86</t>
+          <t>1,02; 4,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,19</t>
+          <t>4,88; 11,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,57</t>
+          <t>1,46; 4,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,24</t>
+          <t>2,43; 6,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,13</t>
+          <t>1,35; 4,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 8,25</t>
+          <t>4,4; 8,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,84</t>
+          <t>1,17; 7,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,74</t>
+          <t>2,83; 10,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 8,3</t>
+          <t>1,84; 8,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,87</t>
+          <t>2,1; 7,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,91</t>
+          <t>0,81; 6,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 14,12</t>
+          <t>3,18; 14,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,35</t>
+          <t>2,08; 6,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,88</t>
+          <t>1,37; 4,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,52</t>
+          <t>0,53; 3,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,63</t>
+          <t>4,12; 10,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,77</t>
+          <t>0,48; 4,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,76</t>
+          <t>1,66; 8,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,69</t>
+          <t>3,01; 9,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,13</t>
+          <t>2,91; 8,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,34</t>
+          <t>1,68; 6,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,3</t>
+          <t>1,82; 7,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,68</t>
+          <t>1,23; 5,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,29</t>
+          <t>1,32; 6,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,48</t>
+          <t>1,48; 4,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,29</t>
+          <t>2,19; 6,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,4</t>
+          <t>2,55; 6,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,96</t>
+          <t>2,57; 6,21</t>
         </is>
       </c>
     </row>
@@ -1277,52 +1277,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,93</t>
+          <t>1,0; 2,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,47</t>
+          <t>1,8; 4,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,03</t>
+          <t>1,57; 4,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,61</t>
+          <t>3,96; 6,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,84</t>
+          <t>2,3; 5,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,14</t>
+          <t>2,37; 5,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,33</t>
+          <t>1,28; 3,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,19</t>
+          <t>4,5; 8,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,62</t>
+          <t>1,89; 3,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,1</t>
+          <t>2,39; 4,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,0</t>
+          <t>4,47; 6,93</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4175</t>
+          <t>0; 4537</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4278</t>
+          <t>0; 2855</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1660,47 +1660,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3275; 10966</t>
+          <t>3286; 10971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>555; 5644</t>
+          <t>553; 5909</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>667; 6488</t>
+          <t>836; 7227</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3721</t>
+          <t>0; 3929</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5002; 16245</t>
+          <t>4714; 15861</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1140; 7042</t>
+          <t>1171; 7601</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1309; 7568</t>
+          <t>1302; 8393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3427</t>
+          <t>0; 3418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10256; 23479</t>
+          <t>10134; 23416</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4211</t>
+          <t>0; 3753</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2658; 9893</t>
+          <t>2709; 10425</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1383; 7633</t>
+          <t>1392; 8338</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4195; 12536</t>
+          <t>4097; 13134</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2629; 10986</t>
+          <t>3071; 10483</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2657; 10521</t>
+          <t>2741; 10783</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1661; 8524</t>
+          <t>1786; 8652</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12364; 28533</t>
+          <t>12437; 28221</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3895; 12145</t>
+          <t>3867; 12590</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6843; 17702</t>
+          <t>6879; 17690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4578; 13502</t>
+          <t>4420; 13576</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18793; 36780</t>
+          <t>19586; 38249</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1301; 7382</t>
+          <t>1258; 7855</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>0; 3782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2974</t>
+          <t>0; 2980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6183; 18552</t>
+          <t>5380; 19107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2027; 9345</t>
+          <t>2070; 9489</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2384; 9189</t>
+          <t>2449; 9202</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1091; 9182</t>
+          <t>1075; 8758</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5575; 26171</t>
+          <t>5899; 27088</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4526; 13993</t>
+          <t>4593; 13743</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3040; 10822</t>
+          <t>3037; 10654</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1295; 8777</t>
+          <t>1318; 9376</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14994; 39952</t>
+          <t>15466; 39962</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>798; 7891</t>
+          <t>792; 7793</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2517; 11334</t>
+          <t>2429; 11773</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5069; 16162</t>
+          <t>5018; 15732</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4803; 13652</t>
+          <t>4885; 14080</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2658; 9953</t>
+          <t>2637; 10264</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2835; 11308</t>
+          <t>2819; 10917</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1665; 8981</t>
+          <t>1938; 9034</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2360; 11395</t>
+          <t>2389; 11134</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4786; 14425</t>
+          <t>4762; 14629</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6958; 18916</t>
+          <t>6596; 18739</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8277; 20814</t>
+          <t>8287; 21630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8668; 20827</t>
+          <t>8976; 21688</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4835; 14749</t>
+          <t>5012; 15030</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8417; 21328</t>
+          <t>8595; 20541</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8157; 21193</t>
+          <t>8253; 21186</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24780; 44047</t>
+          <t>26360; 45360</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11828; 25565</t>
+          <t>12140; 26620</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13359; 27717</t>
+          <t>12767; 27542</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7533; 18987</t>
+          <t>7317; 19810</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34970; 62420</t>
+          <t>34286; 61958</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20139; 37367</t>
+          <t>19548; 36688</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23632; 41632</t>
+          <t>24241; 42138</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18841; 36896</t>
+          <t>18841; 36956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65572; 100011</t>
+          <t>63892; 99037</t>
         </is>
       </c>
     </row>
